--- a/12_Equity_Finance/instances/public_amc_2020_dilution.xlsx
+++ b/12_Equity_Finance/instances/public_amc_2020_dilution.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="331">
   <si>
     <t xml:space="preserve">[ISSUER] — Equity Finance, Dilution, and Capital Structure</t>
   </si>
@@ -48,33 +48,36 @@
     <t xml:space="preserve">Issuer / security:</t>
   </si>
   <si>
+    <t xml:space="preserve">AMC 2020 emergency equity and debt financing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage started:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[date]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Last refreshed:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next financing / shareholder date:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refresh cadence:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weekly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thesis (2-3 sentences):</t>
+  </si>
+  <si>
     <t xml:space="preserve">[fill in]</t>
   </si>
   <si>
-    <t xml:space="preserve">Coverage started:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">[date]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last refreshed:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2020-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Next financing / shareholder date:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refresh cadence:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thesis (2-3 sentences):</t>
-  </si>
-  <si>
     <t xml:space="preserve">COLOR LEGEND</t>
   </si>
   <si>
@@ -958,6 +961,9 @@
   </si>
   <si>
     <t xml:space="preserve">Implied value/share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast base (IS!E5)</t>
   </si>
   <si>
     <t xml:space="preserve">Comparable Companies</t>
@@ -1258,11 +1264,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1712,7 +1718,7 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1720,7 +1726,7 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1728,7 +1734,7 @@
       <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1747,7 +1753,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="6" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -1769,39 +1775,39 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>12</v>
+      <c r="B17" s="4" t="s">
+        <v>13</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1833,43 +1839,43 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I4" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
-      <c r="E5" s="34"/>
+        <v>253</v>
+      </c>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
       <c r="F5" s="34" t="n">
         <f aca="false">E5*(1+Assumptions!C5)</f>
         <v>0</v>
@@ -1889,9 +1895,9 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="35"/>
+        <v>128</v>
+      </c>
+      <c r="C6" s="16"/>
       <c r="D6" s="35" t="str">
         <f aca="false">IFERROR(D5/C5-1,"-")</f>
         <v>-</v>
@@ -1919,11 +1925,11 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
+        <v>254</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
       <c r="F7" s="34" t="n">
         <f aca="false">F5*(1-Assumptions!C6)</f>
         <v>0</v>
@@ -1943,9 +1949,9 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="C8" s="34"/>
+        <v>255</v>
+      </c>
+      <c r="C8" s="23"/>
       <c r="D8" s="34" t="n">
         <f aca="false">D5-D7</f>
         <v>0</v>
@@ -1973,9 +1979,9 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="35"/>
+        <v>130</v>
+      </c>
+      <c r="C9" s="16"/>
       <c r="D9" s="35" t="str">
         <f aca="false">IFERROR(D8/D5,"-")</f>
         <v>-</v>
@@ -2003,11 +2009,11 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
-      <c r="E10" s="34"/>
+        <v>256</v>
+      </c>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="34" t="n">
         <f aca="false">F5*Assumptions!C7</f>
         <v>0</v>
@@ -2027,11 +2033,11 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="C11" s="34"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
+        <v>257</v>
+      </c>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23"/>
       <c r="F11" s="34" t="n">
         <f aca="false">F8-F10</f>
         <v>0</v>
@@ -2051,11 +2057,11 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="35"/>
-      <c r="E12" s="35"/>
+        <v>258</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
       <c r="F12" s="35" t="str">
         <f aca="false">IFERROR(F11/F5,"-")</f>
         <v>-</v>
@@ -2075,11 +2081,11 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
+        <v>259</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
       <c r="F13" s="34" t="n">
         <f aca="false">F5*Assumptions!C10*Assumptions!C9</f>
         <v>0</v>
@@ -2099,11 +2105,11 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+        <v>260</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
       <c r="F14" s="34" t="n">
         <f aca="false">F11-F13</f>
         <v>0</v>
@@ -2123,11 +2129,11 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="34"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
+        <v>261</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
       <c r="F15" s="34" t="n">
         <f aca="false">$E$15</f>
         <v>0</v>
@@ -2147,11 +2153,11 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="34"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
+        <v>262</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
       <c r="F16" s="34" t="n">
         <f aca="false">F14-F15</f>
         <v>0</v>
@@ -2171,11 +2177,11 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="C17" s="34"/>
-      <c r="D17" s="34"/>
-      <c r="E17" s="34"/>
+        <v>263</v>
+      </c>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
       <c r="F17" s="34" t="n">
         <f aca="false">F16*Assumptions!C8</f>
         <v>0</v>
@@ -2195,11 +2201,11 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="C18" s="34"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
+        <v>264</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
       <c r="F18" s="34" t="n">
         <f aca="false">F16-F17</f>
         <v>0</v>
@@ -2219,11 +2225,11 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
+        <v>265</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
       <c r="F19" s="34" t="n">
         <f aca="false">Assumptions!C12</f>
         <v>509.7</v>
@@ -2243,11 +2249,11 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
+        <v>266</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
       <c r="F20" s="34" t="n">
         <f aca="false">IFERROR(F18/F19,"-")</f>
         <v>0</v>
@@ -2291,33 +2297,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
@@ -2327,7 +2333,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -2337,7 +2343,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -2347,7 +2353,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="false">C5+C6+C7</f>
@@ -2372,7 +2378,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -2382,7 +2388,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C10" s="34"/>
       <c r="D10" s="34"/>
@@ -2392,7 +2398,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C11" s="34" t="n">
         <f aca="false">C8+C9+C10</f>
@@ -2417,7 +2423,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -2427,7 +2433,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C13" s="34"/>
       <c r="D13" s="34"/>
@@ -2437,7 +2443,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C14" s="34" t="n">
         <f aca="false">C12+C13</f>
@@ -2462,7 +2468,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C15" s="34"/>
       <c r="D15" s="34"/>
@@ -2472,7 +2478,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C16" s="34" t="n">
         <f aca="false">C14+C15</f>
@@ -2497,7 +2503,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="34"/>
@@ -2507,7 +2513,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="29" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C11-C16-C17</f>
@@ -2556,33 +2562,33 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C5" s="34"/>
       <c r="D5" s="34"/>
@@ -2601,7 +2607,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -2620,7 +2626,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -2630,7 +2636,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C8" s="34" t="n">
         <f aca="false">C5+C6+C7</f>
@@ -2655,7 +2661,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -2665,7 +2671,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C10" s="34" t="n">
         <f aca="false">C8+C9</f>
@@ -2690,7 +2696,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C11" s="34"/>
       <c r="D11" s="34"/>
@@ -2700,7 +2706,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -2710,7 +2716,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C13" s="34" t="n">
         <f aca="false">C10+C11+C12</f>
@@ -2749,7 +2755,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I14"/>
+  <dimension ref="B2:I15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
@@ -2762,32 +2768,32 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C4" s="15" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C5" s="37" t="n">
         <f aca="false">IS!F14*(1-Assumptions!C8)+IS!F13-IS!F5*Assumptions!C10</f>
@@ -2810,7 +2816,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="I5" s="38" t="n">
         <v>0.1</v>
@@ -2818,7 +2824,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C6" s="39" t="n">
         <f aca="false">1/(1+$I$5)^(1)</f>
@@ -2841,7 +2847,7 @@
         <v>0.620921323059155</v>
       </c>
       <c r="H6" s="0" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="I6" s="38" t="n">
         <v>0.025</v>
@@ -2849,7 +2855,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C7" s="40" t="n">
         <f aca="false">C5*C6</f>
@@ -2872,7 +2878,7 @@
         <v>0</v>
       </c>
       <c r="H7" s="0" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="I7" s="40" t="n">
         <f aca="false">G5*(1+I6)/(I5-I6)</f>
@@ -2881,7 +2887,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H8" s="0" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="I8" s="40" t="n">
         <f aca="false">I7*G6</f>
@@ -2890,7 +2896,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H9" s="0" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="I9" s="40" t="n">
         <f aca="false">SUM(C7:G7)</f>
@@ -2899,7 +2905,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H10" s="0" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="I10" s="41" t="n">
         <f aca="false">I8+I9</f>
@@ -2908,7 +2914,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H11" s="0" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I11" s="42" t="n">
         <v>0</v>
@@ -2916,7 +2922,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H12" s="0" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="I12" s="41" t="n">
         <f aca="false">I10-I11</f>
@@ -2925,7 +2931,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H13" s="0" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="I13" s="42" t="n">
         <v>1</v>
@@ -2933,11 +2939,20 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H14" s="0" t="s">
-        <v>305</v>
-      </c>
-      <c r="I14" s="41" t="n">
-        <f aca="false">I12/I13</f>
-        <v>0</v>
+        <v>306</v>
+      </c>
+      <c r="I14" s="41" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"n/a - no forecast base",I12/I13)</f>
+        <v>n/a - no forecast base</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="0" t="s">
+        <v>307</v>
+      </c>
+      <c r="I15" s="2" t="str">
+        <f aca="false">IF(OR(IS!E5="",IS!E5=0),"MISSING - the DCF cannot value anything","present")</f>
+        <v>MISSING - the DCF cannot value anything</v>
       </c>
     </row>
   </sheetData>
@@ -2966,36 +2981,36 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>314</v>
+      <c r="B5" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C5" s="43" t="n">
         <v>0</v>
@@ -3017,8 +3032,8 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="3" t="s">
-        <v>314</v>
+      <c r="B6" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C6" s="43" t="n">
         <v>0</v>
@@ -3040,8 +3055,8 @@
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="3" t="s">
-        <v>314</v>
+      <c r="B7" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C7" s="43" t="n">
         <v>0</v>
@@ -3063,8 +3078,8 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="3" t="s">
-        <v>314</v>
+      <c r="B8" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C8" s="43" t="n">
         <v>0</v>
@@ -3086,8 +3101,8 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="3" t="s">
-        <v>314</v>
+      <c r="B9" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C9" s="43" t="n">
         <v>0</v>
@@ -3109,8 +3124,8 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="3" t="s">
-        <v>314</v>
+      <c r="B10" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C10" s="43" t="n">
         <v>0</v>
@@ -3132,8 +3147,8 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="3" t="s">
-        <v>314</v>
+      <c r="B11" s="4" t="s">
+        <v>316</v>
       </c>
       <c r="C11" s="43" t="n">
         <v>0</v>
@@ -3156,7 +3171,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C13" s="41" t="n">
         <f aca="false">MEDIAN(C5:C12)</f>
@@ -3209,12 +3224,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="28" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>0.015</v>
@@ -3237,19 +3252,19 @@
         <v>0.08</v>
       </c>
       <c r="C5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G5" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3257,19 +3272,19 @@
         <v>0.09</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3277,19 +3292,19 @@
         <v>0.1</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3297,19 +3312,19 @@
         <v>0.11</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3317,19 +3332,19 @@
         <v>0.12</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="G9" s="29" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -3360,42 +3375,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="32" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C5" s="32" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D5" s="32" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E5" s="32" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3489,7 +3504,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -3498,10 +3513,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B4" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
@@ -3509,10 +3524,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
@@ -3520,10 +3535,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="10" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
@@ -3531,10 +3546,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
@@ -3542,10 +3557,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
@@ -3553,10 +3568,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B9" s="10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
@@ -3564,10 +3579,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11"/>
@@ -3575,7 +3590,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="12"/>
       <c r="D12" s="12"/>
@@ -3584,19 +3599,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3604,10 +3619,10 @@
         <v>1</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3615,10 +3630,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="14" t="s">
         <v>43</v>
-      </c>
-      <c r="F15" s="14" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3626,10 +3641,10 @@
         <v>3</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3637,10 +3652,10 @@
         <v>4</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3648,15 +3663,15 @@
         <v>5</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="12"/>
@@ -3665,19 +3680,19 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F21" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3685,10 +3700,10 @@
         <v>1</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,10 +3711,10 @@
         <v>2</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3707,10 +3722,10 @@
         <v>3</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3718,10 +3733,10 @@
         <v>4</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3729,15 +3744,15 @@
         <v>5</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
@@ -3746,19 +3761,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E29" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F29" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3766,10 +3781,10 @@
         <v>1</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3777,10 +3792,10 @@
         <v>2</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3788,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3799,10 +3814,10 @@
         <v>4</v>
       </c>
       <c r="C33" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3810,15 +3825,15 @@
         <v>5</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="12" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -3827,19 +3842,19 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D37" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F37" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3847,10 +3862,10 @@
         <v>1</v>
       </c>
       <c r="C38" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3858,10 +3873,10 @@
         <v>2</v>
       </c>
       <c r="C39" s="0" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3869,10 +3884,10 @@
         <v>3</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3880,10 +3895,10 @@
         <v>4</v>
       </c>
       <c r="C41" s="0" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3891,15 +3906,15 @@
         <v>5</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C44" s="12"/>
       <c r="D44" s="12"/>
@@ -3908,19 +3923,19 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D45" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F45" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3928,10 +3943,10 @@
         <v>1</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3939,10 +3954,10 @@
         <v>2</v>
       </c>
       <c r="C47" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3950,10 +3965,10 @@
         <v>3</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3961,10 +3976,10 @@
         <v>4</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3972,15 +3987,15 @@
         <v>5</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="12"/>
       <c r="D52" s="12"/>
@@ -3989,19 +4004,19 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="13" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D53" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F53" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4009,10 +4024,10 @@
         <v>1</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4020,10 +4035,10 @@
         <v>2</v>
       </c>
       <c r="C55" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4031,10 +4046,10 @@
         <v>3</v>
       </c>
       <c r="C56" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4042,10 +4057,10 @@
         <v>4</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4053,15 +4068,15 @@
         <v>5</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
@@ -4070,47 +4085,47 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C61" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D61" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C62" s="0" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E62" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="0" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D63" s="0" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="0" t="s">
         <v>87</v>
-      </c>
-      <c r="C63" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="D63" s="0" t="s">
-        <v>89</v>
-      </c>
-      <c r="E63" s="0" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -4187,7 +4202,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4199,68 +4214,68 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D5" s="0" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D6" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D7" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D8" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D9" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4443,7 +4458,7 @@
   <sheetData>
     <row r="2" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="9" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" s="9"/>
       <c r="D2" s="9"/>
@@ -4456,87 +4471,87 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J5" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>112</v>
+      </c>
+      <c r="D6" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" s="14" t="s">
         <v>110</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>112</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J7" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J8" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4671,36 +4686,36 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15"/>
       <c r="B4" s="15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H4" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C5" s="16" t="n">
         <v>0</v>
@@ -4718,35 +4733,35 @@
         <v>0</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="s">
         <v>129</v>
-      </c>
-      <c r="C6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="17" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C7" s="16" t="n">
         <v>0</v>
@@ -4764,12 +4779,12 @@
         <v>0</v>
       </c>
       <c r="H7" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0</v>
@@ -4787,12 +4802,12 @@
         <v>0</v>
       </c>
       <c r="H8" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C9" s="18" t="n">
         <v>0</v>
@@ -4810,12 +4825,12 @@
         <v>0</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C10" s="18" t="n">
         <v>0</v>
@@ -4833,12 +4848,12 @@
         <v>0</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" s="18" t="n">
         <v>0</v>
@@ -4856,12 +4871,12 @@
         <v>0</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="19" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E19</f>
@@ -4884,12 +4899,12 @@
         <v>509.7</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0</v>
@@ -4907,12 +4922,12 @@
         <v>0</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>0</v>
@@ -4930,7 +4945,7 @@
         <v>0</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -4960,37 +4975,37 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="0" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="E4" s="15" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="21" t="n">
         <v>100</v>
@@ -5003,12 +5018,12 @@
         <v>125</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" s="21" t="n">
         <v>5</v>
@@ -5021,12 +5036,12 @@
         <v>20</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>20</v>
@@ -5039,12 +5054,12 @@
         <v>164.7</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>25</v>
@@ -5057,12 +5072,12 @@
         <v>100</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C9" s="23" t="n">
         <v>100</v>
@@ -5075,12 +5090,12 @@
         <v>500</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C10" s="25" t="n">
         <v>10</v>
@@ -5093,12 +5108,12 @@
         <v>5</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>11</v>
@@ -5111,12 +5126,12 @@
         <v>3.07</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="23" t="n">
         <v>5</v>
@@ -5129,12 +5144,12 @@
         <v>15.2</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="16" t="n">
         <v>0.35</v>
@@ -5147,12 +5162,12 @@
         <v>0.35</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="16" t="n">
         <v>0.1</v>
@@ -5165,17 +5180,17 @@
         <v>0.1</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="22" t="n">
         <f aca="false">IFERROR(C9/C10,0)</f>
@@ -5192,7 +5207,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">SUM(C5:C8)+C18</f>
@@ -5209,7 +5224,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">IFERROR(C5/C19,0)</f>
@@ -5226,7 +5241,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C21" s="27" t="n">
         <f aca="false">1-C20</f>
@@ -5243,7 +5258,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C22" s="27" t="n">
         <f aca="false">IFERROR(C6/C19,0)</f>
@@ -5260,7 +5275,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">C7*C11</f>
@@ -5277,7 +5292,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C24" s="24" t="n">
         <f aca="false">C23-C12</f>
@@ -5294,7 +5309,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">C19-C5-C6-C7-C8-C18</f>
@@ -5311,7 +5326,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="29" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -5341,26 +5356,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="E4" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C5</f>
@@ -5371,12 +5386,12 @@
         <v>125</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C6" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C8</f>
@@ -5387,12 +5402,12 @@
         <v>100</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>12</v>
@@ -5401,12 +5416,12 @@
         <v>10</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" s="25" t="n">
         <v>9</v>
@@ -5415,12 +5430,12 @@
         <v>3</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C9" s="16" t="n">
         <v>0.9</v>
@@ -5429,12 +5444,12 @@
         <v>0.196</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0.02</v>
@@ -5443,12 +5458,12 @@
         <v>0.08</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C13" s="24" t="n">
         <f aca="false">IFERROR((C5*C7+C6*C8)/(C5+C6),0)</f>
@@ -5461,7 +5476,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C14" s="24" t="n">
         <f aca="false">C7-C13</f>
@@ -5474,7 +5489,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C15" s="27" t="n">
         <f aca="false">IFERROR(1-C8/C7,0)</f>
@@ -5487,7 +5502,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">C6*C9</f>
@@ -5500,7 +5515,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">C16*C8</f>
@@ -5513,7 +5528,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C18" s="24" t="n">
         <f aca="false">(C6-C16)*C8*C10</f>
@@ -5526,7 +5541,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C19" s="24" t="n">
         <f aca="false">C17-C18</f>
@@ -5539,7 +5554,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="29" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>
@@ -5569,26 +5584,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>140</v>
-      </c>
       <c r="E4" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C9</f>
@@ -5599,12 +5614,12 @@
         <v>500</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C6" s="26" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!C10</f>
@@ -5615,12 +5630,12 @@
         <v>5</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C7" s="25" t="n">
         <v>12</v>
@@ -5629,12 +5644,12 @@
         <v>4</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C8" s="16" t="n">
         <v>0.04</v>
@@ -5643,12 +5658,12 @@
         <v>0.08</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C9" s="30" t="n">
         <v>3</v>
@@ -5657,12 +5672,12 @@
         <v>1</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C10" s="16" t="n">
         <v>0.05</v>
@@ -5671,12 +5686,12 @@
         <v>0.15</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C11" s="25" t="n">
         <v>9.5</v>
@@ -5685,12 +5700,12 @@
         <v>3.5</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">IFERROR(C5/C6,0)</f>
@@ -5703,7 +5718,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="0" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C15" s="22" t="n">
         <f aca="false">IFERROR(C5/C11,0)</f>
@@ -5716,7 +5731,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="0" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C16" s="24" t="n">
         <f aca="false">C14*C7</f>
@@ -5729,7 +5744,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="0" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C17" s="24" t="n">
         <f aca="false">C5*(1+C10)</f>
@@ -5742,7 +5757,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="0" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C18" s="31" t="n">
         <f aca="false">IFERROR(C16/C5,0)</f>
@@ -5755,7 +5770,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">C15-C14</f>
@@ -5768,7 +5783,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C20" s="24" t="n">
         <f aca="false">C5*C8</f>
@@ -5781,7 +5796,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="29" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5811,26 +5826,26 @@
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="0" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C5" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E25</f>
@@ -5841,12 +5856,12 @@
         <v>PASS</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="0" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C6" s="32" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E20+'Cap Table &amp; Dilution'!E21-1</f>
@@ -5857,12 +5872,12 @@
         <v>PASS</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C7" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E21</f>
@@ -5873,12 +5888,12 @@
         <v>BREACH</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="0" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E22</f>
@@ -5889,12 +5904,12 @@
         <v>PASS</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C9" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E24</f>
@@ -5905,12 +5920,12 @@
         <v>PASS</v>
       </c>
       <c r="E9" s="0" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="0" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C10" s="32" t="n">
         <f aca="false">'Rights Offering'!C13-(('Rights Offering'!C5*'Rights Offering'!C7+'Rights Offering'!C6*'Rights Offering'!C8)/('Rights Offering'!C5+'Rights Offering'!C6))</f>
@@ -5921,12 +5936,12 @@
         <v>PASS</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="0" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C11" s="24" t="n">
         <f aca="false">'Rights Offering'!C14</f>
@@ -5937,12 +5952,12 @@
         <v>PASS</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="0" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C12" s="27" t="n">
         <f aca="false">'Rights Offering'!D9</f>
@@ -5953,12 +5968,12 @@
         <v>BREACH</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="0" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C13" s="32" t="n">
         <f aca="false">'Convertible Securities'!C14-'Cap Table &amp; Dilution'!C18</f>
@@ -5969,12 +5984,12 @@
         <v>PASS</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="0" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C14" s="22" t="n">
         <f aca="false">'Convertible Securities'!D19</f>
@@ -5985,12 +6000,12 @@
         <v>REVIEW</v>
       </c>
       <c r="E14" s="0" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C16" s="33" t="str">
         <f aca="false">IF(COUNTIF(D5:D14,"FAIL")+COUNTIF(D5:D14,"BREACH")&gt;0,"BREACH",IF(COUNTIF(D5:D14,"REVIEW")&gt;0,"REVIEW","PASS"))</f>
@@ -5999,12 +6014,12 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="0" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C19" s="22" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E19</f>
@@ -6013,7 +6028,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="0" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E21</f>
@@ -6022,7 +6037,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="0" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C21" s="24" t="n">
         <f aca="false">'Cap Table &amp; Dilution'!E24</f>
@@ -6031,7 +6046,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="0" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C22" s="26" t="n">
         <f aca="false">'Rights Offering'!C13</f>
@@ -6040,7 +6055,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="0" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="24" t="n">
         <f aca="false">'Rights Offering'!C19</f>
@@ -6049,7 +6064,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="0" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C24" s="22" t="n">
         <f aca="false">'Convertible Securities'!C14</f>
@@ -6058,7 +6073,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="0" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C25" s="22" t="n">
         <f aca="false">'Convertible Securities'!D15</f>
@@ -6067,7 +6082,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="0" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C26" s="24" t="n">
         <f aca="false">'Convertible Securities'!D17</f>
